--- a/docs/prompts-sessions.xlsx
+++ b/docs/prompts-sessions.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W116"/>
+  <dimension ref="A1:W141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -445,7 +445,7 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="21" customWidth="1" min="20" max="20"/>
     <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="63" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
@@ -11373,32 +11373,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1e3ca7a9-a840-4249-a554-0f56781a1740</t>
+          <t>97e97192-f350-4702-8e44-10f417c6cc8a</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20260924T160346-94745</t>
+          <t>orch-20260926T223505-376430</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>414f8cf</t>
+          <t>1f736c7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-09-24T16:03:46+03:00</t>
+          <t>2026-09-26T22:35:07+03:00</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-24T16:11:12+03:00</t>
+          <t>2026-09-26T22:42:08+03:00</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -11441,65 +11441,69 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>/backend-dev examples/single-us/US-tags.md --runner 97160f9247edc94dfd81cf44</t>
+          <t>/backend-dev examples/single-us/US-tags.md --runner dd693dcb5e0707a200d962a2</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-00-review.md</t>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-00-review.md</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="R106" t="n">
-        <v>3359737</v>
+        <v>3332125</v>
       </c>
       <c r="S106" t="n">
-        <v>43372</v>
+        <v>40857</v>
       </c>
       <c r="T106" t="n">
-        <v>2.5735112</v>
+        <v>2.42263</v>
       </c>
       <c r="U106" t="n">
-        <v>439562</v>
+        <v>418941</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="W106" t="inlineStr"/>
+          <t>violation: runner-owned file changed: docs/commit-reviews.md;</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>5517e77</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ce45db66-6092-46a3-8db7-9ecf280d915e</t>
+          <t>f69fe676-18a1-4449-890c-7a15d47b44f0</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20260924T161844-98093</t>
+          <t>orch-20260926T224717-382863</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>a71a377</t>
+          <t>1f736c7</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-09-24T16:18:47+03:00</t>
+          <t>2026-09-26T22:47:18+03:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-24T16:21:22+03:00</t>
+          <t>2026-09-26T22:49:28+03:00</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -11514,7 +11518,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -11538,70 +11542,74 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>/backend-dev examples/single-us/US-tags.md --runner 86451615feb94c52ac9b019c</t>
+          <t>/backend-dev examples/single-us/US-tags.md --runner bfa42dea12428bc61a88de91</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-00-review.md</t>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-00-review.md</t>
         </is>
       </c>
       <c r="Q107" t="n">
         <v>38</v>
       </c>
       <c r="R107" t="n">
-        <v>1359188</v>
+        <v>1085802</v>
       </c>
       <c r="S107" t="n">
-        <v>12722</v>
+        <v>13917</v>
       </c>
       <c r="T107" t="n">
-        <v>1.2770704</v>
+        <v>0.876815</v>
       </c>
       <c r="U107" t="n">
-        <v>150951</v>
+        <v>127624</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W107" t="inlineStr"/>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>5517e77</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3bfaaf87-44d9-4d25-a500-0dc7b8082a93</t>
+          <t>cf20ee51-3544-4dcc-8953-5ad8b6db8575</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20260924T161844-98093</t>
+          <t>orch-20260926T224717-382863</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>a71a377</t>
+          <t>1f736c7</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-09-24T16:21:24+03:00</t>
+          <t>2026-09-26T22:49:30+03:00</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-24T16:22:38+03:00</t>
+          <t>2026-09-26T22:54:40+03:00</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>backend-dev</t>
+          <t>frontend-dev</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11611,17 +11619,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>phase-01</t>
+          <t>phase-00-plan</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>plan</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -11634,75 +11642,79 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+          <t>Plan frontend from examples/single-us/US-tags.md</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>/backend-dev examples/single-us/US-tags.md --runner 86451615feb94c52ac9b019c</t>
+          <t>/frontend-dev examples/single-us/US-tags.md specs/002-us-tags-backend/contracts/openapi.yaml --runner 81943453a18cf37230c0f63d</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-00-review.md</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="R108" t="n">
-        <v>620935</v>
+        <v>2903300</v>
       </c>
       <c r="S108" t="n">
-        <v>5800</v>
+        <v>31809</v>
       </c>
       <c r="T108" t="n">
-        <v>0.5523610000000001</v>
+        <v>2.0136014</v>
       </c>
       <c r="U108" t="n">
-        <v>69606</v>
+        <v>307503</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W108" t="inlineStr"/>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>b772ca7</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>85ec4372-37e1-4cbc-8abe-fc2418e1a031</t>
+          <t>e6e6ba79-b35a-4e7d-bcd9-5b98dea11178</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20260924T161844-98093</t>
+          <t>orch-20260926T224717-382863</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>a71a377</t>
+          <t>1f736c7</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-09-24T16:22:43+03:00</t>
+          <t>2026-09-26T22:54:41+03:00</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-24T16:24:16+03:00</t>
+          <t>2026-09-26T22:55:44+03:00</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>backend-dev</t>
+          <t>frontend-dev</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -11712,17 +11724,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>phase-01</t>
+          <t>phase-00-plan</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>implement</t>
+          <t>plan</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -11733,97 +11745,97 @@
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
-        </is>
-      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
-          <t>/backend-dev examples/single-us/US-tags.md --runner 86451615feb94c52ac9b019c</t>
+          <t>/frontend-dev examples/single-us/US-tags.md specs/002-us-tags-backend/contracts/openapi.yaml --runner 81943453a18cf37230c0f63d</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-00-review.md</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R109" t="n">
-        <v>600747</v>
+        <v>438653</v>
       </c>
       <c r="S109" t="n">
-        <v>7874</v>
+        <v>4024</v>
       </c>
       <c r="T109" t="n">
-        <v>0.6108397999999999</v>
+        <v>0.4054106</v>
       </c>
       <c r="U109" t="n">
-        <v>88976</v>
+        <v>60089</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W109" t="inlineStr"/>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>b772ca7</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01702234-ea3f-41bd-bbff-244df7cc06d9</t>
+          <t>ee94bcf0-feea-4fca-96ca-d0616845a912</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20260924T162625-101563</t>
+          <t>orch-20260926T225858-388446</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>caf40ba</t>
+          <t>91be504</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-09-24T16:26:28+03:00</t>
+          <t>2026-09-26T22:59:02+03:00</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-24T16:34:10+03:00</t>
+          <t>2026-09-26T22:59:34+03:00</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>backend-dev</t>
+          <t>orchestrator</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>dev</t>
+          <t>plan</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>phase-01</t>
+          <t>plan</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>implement</t>
+          <t>orchestrator</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -11836,70 +11848,74 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+          <t>Order the stories of examples/single-us/US-tags.md across layers</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>/backend-dev examples/single-us/US-tags.md --runner 304702a8f9e6acce8ebd0a40</t>
+          <t>/orchestrator plan examples/single-us/US-tags.md --runner 5cca14f33a6daadc672f6fce</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+          <t>loops/*/state/002-us-tags/phases.json</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="R110" t="n">
-        <v>3234266</v>
+        <v>251265</v>
       </c>
       <c r="S110" t="n">
-        <v>19369</v>
+        <v>2517</v>
       </c>
       <c r="T110" t="n">
-        <v>1.6177836</v>
+        <v>0.2413454</v>
       </c>
       <c r="U110" t="n">
-        <v>457953</v>
+        <v>30053</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W110" t="inlineStr"/>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>840a8b8</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>210e4286-d479-4dea-a9f9-57dbc44f55ae</t>
+          <t>ea4043c7-2fe8-407d-a6dc-c09430e9c15e</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>20260924T163914-107873</t>
+          <t>orch-20260926T225858-388446</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>caf40ba</t>
+          <t>91be504</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-09-24T16:39:17+03:00</t>
+          <t>2026-09-26T22:59:36+03:00</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-24T16:41:20+03:00</t>
+          <t>2026-09-26T23:01:06+03:00</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -11914,7 +11930,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -11924,7 +11940,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>implement</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -11937,95 +11953,99 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+          <t>Add tags to a task, read them back, filter the task list by tag and remove a tag, with validation (1–30 characters, case-insensitive, at most 10 per task).</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>/backend-dev examples/single-us/US-tags.md --runner 8dd086dac613f66e2bd8e45f</t>
+          <t>/backend-dev examples/single-us/US-tags.md --runner ffbeff507579eefa61df9fd6</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-01-review.md</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R111" t="n">
-        <v>635640</v>
+        <v>779915</v>
       </c>
       <c r="S111" t="n">
-        <v>4266</v>
+        <v>8525</v>
       </c>
       <c r="T111" t="n">
-        <v>0.4795694000000001</v>
+        <v>0.6299294000000002</v>
       </c>
       <c r="U111" t="n">
-        <v>118987</v>
+        <v>87539</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W111" t="inlineStr"/>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>dbe139e</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>283a9f7b-6458-4b49-a26e-a606c25b4840</t>
+          <t>90173efa-debc-4995-9bae-1df8951608ff</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>20260924T163914-107873</t>
+          <t>orch-20260926T225858-388446</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>caf40ba</t>
+          <t>91be504</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-09-24T16:41:41+03:00</t>
+          <t>2026-09-26T23:01:07+03:00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-24T16:43:42+03:00</t>
+          <t>2026-09-26T23:06:08+03:00</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>testing</t>
+          <t>backend-dev</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>phase</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>backend-dev:phase-01</t>
+          <t>phase-01</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>implement</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -12038,95 +12058,99 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+          <t>Add tags to a task, read them back, filter the task list by tag and remove a tag, with validation (1–30 characters, case-insensitive, at most 10 per task).</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>/testing phase backend-dev phase-01 --runner 8dd086dac613f66e2bd8e45f</t>
+          <t>/backend-dev examples/single-us/US-tags.md --runner ffbeff507579eefa61df9fd6</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-01.md; loops/testing/runs/001-us-tags/backend-dev/phase-01/attempt-1/unit/unit-result.json</t>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-01-review.md</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="R112" t="n">
-        <v>1156172</v>
+        <v>3770188</v>
       </c>
       <c r="S112" t="n">
-        <v>10454</v>
+        <v>30146</v>
       </c>
       <c r="T112" t="n">
-        <v>0.7427248000000002</v>
+        <v>3.4131388</v>
       </c>
       <c r="U112" t="n">
-        <v>116637</v>
+        <v>298205</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>dbe139e</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>d27f1f22-4e72-4b71-ba1d-7e7bf7fcfce0</t>
+          <t>66a2329a-9f3b-49b3-a7b1-0672c7f438a7</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>20260924T163914-107873</t>
+          <t>orch-20260926T225858-388446</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>caf40ba</t>
+          <t>91be504</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-09-24T16:43:45+03:00</t>
+          <t>2026-09-26T23:06:30+03:00</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-24T16:44:34+03:00</t>
+          <t>2026-09-26T23:10:14+03:00</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>backend-dev</t>
+          <t>testing</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>dev</t>
+          <t>phase</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>phase-01</t>
+          <t>backend-dev:phase-01</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>test</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -12139,33 +12163,33 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+          <t>Add tags to a task, read them back, filter the task list by tag and remove a tag, with validation (1–30 characters, case-insensitive, at most 10 per task).</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>/backend-dev examples/single-us/US-tags.md --runner 8dd086dac613f66e2bd8e45f</t>
+          <t>/testing phase backend-dev phase-01 --runner ffbeff507579eefa61df9fd6</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-01.md; loops/testing/runs/002-us-tags/backend-dev/phase-01/attempt-1/unit/unit-result.json</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="R113" t="n">
-        <v>380694</v>
+        <v>1233749</v>
       </c>
       <c r="S113" t="n">
-        <v>3431</v>
+        <v>20594</v>
       </c>
       <c r="T113" t="n">
-        <v>0.3270622</v>
+        <v>1.1813428</v>
       </c>
       <c r="U113" t="n">
-        <v>44308</v>
+        <v>222287</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -12177,32 +12201,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>51c04a05-8258-4f75-9027-a5da5f5817cb</t>
+          <t>9e049abe-9a5a-4419-8743-a09da21170e6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>20260924T163914-107873</t>
+          <t>orch-20260926T225858-388446</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>caf40ba</t>
+          <t>91be504</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-09-24T16:44:36+03:00</t>
+          <t>2026-09-26T23:10:16+03:00</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-24T16:46:12+03:00</t>
+          <t>2026-09-26T23:11:01+03:00</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -12217,7 +12241,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -12227,11 +12251,11 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>retry</t>
+          <t>close</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -12240,99 +12264,103 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+          <t>Add tags to a task, read them back, filter the task list by tag and remove a tag, with validation (1–30 characters, case-insensitive, at most 10 per task).</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>/backend-dev examples/single-us/US-tags.md --runner 8dd086dac613f66e2bd8e45f</t>
+          <t>/backend-dev examples/single-us/US-tags.md --runner ffbeff507579eefa61df9fd6</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md; loops/backend-dev/outputs/001-us-tags/phase-01-report.md</t>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-01-review.md</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="R114" t="n">
-        <v>807203</v>
+        <v>303500</v>
       </c>
       <c r="S114" t="n">
-        <v>6053</v>
+        <v>2840</v>
       </c>
       <c r="T114" t="n">
-        <v>0.6097760000000001</v>
+        <v>0.4781732</v>
       </c>
       <c r="U114" t="n">
-        <v>91836</v>
+        <v>43268</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W114" t="inlineStr"/>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>dbe139e</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>83aba213-08c7-491a-a2cf-c23f78f0d607</t>
+          <t>d5228fb3-0193-4317-aa5f-0d63c8225c46</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>20260924T163914-107873</t>
+          <t>orch-20260926T225858-388446</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>caf40ba</t>
+          <t>91be504</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-09-24T16:46:33+03:00</t>
+          <t>2026-09-26T23:11:04+03:00</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-24T16:47:35+03:00</t>
+          <t>2026-09-26T23:13:33+03:00</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>testing</t>
+          <t>frontend-dev</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>phase</t>
+          <t>dev</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>backend-dev:phase-01</t>
+          <t>phase-01</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>review</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -12341,141 +12369,2706 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+          <t>On `/tasks`, show each task's tags, add one or more tags to a task, remove a tag, and filter the list by tag.</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>/testing phase backend-dev phase-01 --runner 8dd086dac613f66e2bd8e45f</t>
+          <t>/frontend-dev examples/single-us/US-tags.md loops/backend-dev/outputs/openapi.json --runner 77a203b5fc0119604072a1e2</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>loops/backend-dev/outputs/001-us-tags/phase-01.md; loops/testing/runs/001-us-tags/backend-dev/phase-01/attempt-2/unit/unit-result.json</t>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-01-review.md</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="R115" t="n">
-        <v>521714</v>
+        <v>1315652</v>
       </c>
       <c r="S115" t="n">
-        <v>5707</v>
+        <v>9954</v>
       </c>
       <c r="T115" t="n">
-        <v>0.4796134</v>
+        <v>0.8726432000000001</v>
       </c>
       <c r="U115" t="n">
-        <v>57503</v>
+        <v>147325</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W115" t="inlineStr"/>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>13ad7c5</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>e47ecef3-ccbf-4dd1-9b11-7d5a3942b564</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:13:34+03:00</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:16:09+03:00</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>implement</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>On `/tasks`, show each task's tags, add one or more tags to a task, remove a tag, and filter the list by tag.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>/frontend-dev examples/single-us/US-tags.md loops/backend-dev/outputs/openapi.json --runner 77a203b5fc0119604072a1e2</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-01-review.md</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>56</v>
+      </c>
+      <c r="R116" t="n">
+        <v>1972426</v>
+      </c>
+      <c r="S116" t="n">
+        <v>15124</v>
+      </c>
+      <c r="T116" t="n">
+        <v>1.238766599999999</v>
+      </c>
+      <c r="U116" t="n">
+        <v>152700</v>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>13ad7c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>42d4ac9a-a9c2-4e84-b957-fbfb45790985</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:16:17+03:00</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:20:30+03:00</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>frontend-dev:phase-01</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>On `/tasks`, show each task's tags, add one or more tags to a task, remove a tag, and filter the list by tag.</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>/testing phase frontend-dev phase-01 --runner 77a203b5fc0119604072a1e2</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-01.md; loops/testing/runs/002-us-tags/frontend-dev/phase-01/attempt-1/unit/unit-result.json</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>94</v>
+      </c>
+      <c r="R117" t="n">
+        <v>3383144</v>
+      </c>
+      <c r="S117" t="n">
+        <v>19420</v>
+      </c>
+      <c r="T117" t="n">
+        <v>1.6401634</v>
+      </c>
+      <c r="U117" t="n">
+        <v>249692</v>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>d8f91352-90b1-41da-8d44-732d9df2400c</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:20:32+03:00</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:24:05+03:00</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>On `/tasks`, show each task's tags, add one or more tags to a task, remove a tag, and filter the list by tag.</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>/frontend-dev examples/single-us/US-tags.md loops/backend-dev/outputs/openapi.json --runner 77a203b5fc0119604072a1e2</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-01-review.md</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>16</v>
+      </c>
+      <c r="R118" t="n">
+        <v>387236</v>
+      </c>
+      <c r="S118" t="n">
+        <v>3272</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.4715028</v>
+      </c>
+      <c r="U118" t="n">
+        <v>60919</v>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>13ad7c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cd4fd9a9-d1df-4c43-abb9-db60a3e7b6dd</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:24:07+03:00</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:25:25+03:00</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>phase-02</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>The generated swagger matches the tags contract, and the whole backend test suite and the coverage gate still pass.</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 017057521736e5c1ff88c8df</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-02-review.md</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>28</v>
+      </c>
+      <c r="R119" t="n">
+        <v>641933</v>
+      </c>
+      <c r="S119" t="n">
+        <v>6363</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.4938614000000001</v>
+      </c>
+      <c r="U119" t="n">
+        <v>68314</v>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>45ed52e</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>6b837034-1456-41ea-b432-34d3050f5b87</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:25:26+03:00</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:30:24+03:00</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>phase-02</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>implement</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>The generated swagger matches the tags contract, and the whole backend test suite and the coverage gate still pass.</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 017057521736e5c1ff88c8df</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-02-review.md</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>60</v>
+      </c>
+      <c r="R120" t="n">
+        <v>2530315</v>
+      </c>
+      <c r="S120" t="n">
+        <v>18479</v>
+      </c>
+      <c r="T120" t="n">
+        <v>1.561074</v>
+      </c>
+      <c r="U120" t="n">
+        <v>295270</v>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>45ed52e</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>06026f73-1438-4039-9fbb-650a96c51226</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:30:46+03:00</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:34:56+03:00</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>backend-dev:phase-02</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>The generated swagger matches the tags contract, and the whole backend test suite and the coverage gate still pass.</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>/testing phase backend-dev phase-02 --runner 017057521736e5c1ff88c8df</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-02.md; loops/testing/runs/002-us-tags/backend-dev/phase-02/attempt-1/unit/unit-result.json</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>62</v>
+      </c>
+      <c r="R121" t="n">
+        <v>2213968</v>
+      </c>
+      <c r="S121" t="n">
+        <v>23101</v>
+      </c>
+      <c r="T121" t="n">
+        <v>1.4557962</v>
+      </c>
+      <c r="U121" t="n">
+        <v>247550</v>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>c5d4032d-2eb5-4598-ad7c-95d1766f9dd0</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:34:57+03:00</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:36:26+03:00</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>phase-02</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>The generated swagger matches the tags contract, and the whole backend test suite and the coverage gate still pass.</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 017057521736e5c1ff88c8df</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/002-us-tags/phase-02-review.md</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>30</v>
+      </c>
+      <c r="R122" t="n">
+        <v>801653</v>
+      </c>
+      <c r="S122" t="n">
+        <v>7112</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.6964268000000001</v>
+      </c>
+      <c r="U122" t="n">
+        <v>84959</v>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>45ed52e</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20eb43f2-f2ad-4020-99c2-50d5d558b7da</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:36:28+03:00</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:37:45+03:00</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>phase-02</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>1</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Check the tag UI against the UI contract and the swagger, and finish with a clean build.</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>/frontend-dev examples/single-us/US-tags.md loops/backend-dev/outputs/openapi.json --runner 4a6c2564ec4b8b25f8c7b7a4</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-02-review.md</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>28</v>
+      </c>
+      <c r="R123" t="n">
+        <v>652201</v>
+      </c>
+      <c r="S123" t="n">
+        <v>6389</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.5097262000000001</v>
+      </c>
+      <c r="U123" t="n">
+        <v>74939</v>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>76bd8e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>9bb2c683-0517-4568-858e-c5c37825e41f</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:37:46+03:00</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:39:52+03:00</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>phase-02</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>implement</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Check the tag UI against the UI contract and the swagger, and finish with a clean build.</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>/frontend-dev examples/single-us/US-tags.md loops/backend-dev/outputs/openapi.json --runner 4a6c2564ec4b8b25f8c7b7a4</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-02-review.md</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>44</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1244263</v>
+      </c>
+      <c r="S124" t="n">
+        <v>8194</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.7773167999999998</v>
+      </c>
+      <c r="U124" t="n">
+        <v>123274</v>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>76bd8e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>0bfd174f-a810-416c-9b6d-f85f6c4b68fd</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:40:00+03:00</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:43:48+03:00</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>frontend-dev:phase-02</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Check the tag UI against the UI contract and the swagger, and finish with a clean build.</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>/testing phase frontend-dev phase-02 --runner 4a6c2564ec4b8b25f8c7b7a4</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-02.md; loops/testing/runs/002-us-tags/frontend-dev/phase-02/attempt-1/unit/unit-result.json</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>76</v>
+      </c>
+      <c r="R125" t="n">
+        <v>2542916</v>
+      </c>
+      <c r="S125" t="n">
+        <v>20180</v>
+      </c>
+      <c r="T125" t="n">
+        <v>1.46064</v>
+      </c>
+      <c r="U125" t="n">
+        <v>224910</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>fb32ca4a-3089-4928-abd6-35692b921033</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:43:49+03:00</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:45:14+03:00</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>phase-02</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Check the tag UI against the UI contract and the swagger, and finish with a clean build.</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>/frontend-dev examples/single-us/US-tags.md loops/backend-dev/outputs/openapi.json --runner 4a6c2564ec4b8b25f8c7b7a4</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>loops/frontend-dev/outputs/002-us-tags/phase-02-review.md</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>36</v>
+      </c>
+      <c r="R126" t="n">
+        <v>948382</v>
+      </c>
+      <c r="S126" t="n">
+        <v>6318</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.6994958000000001</v>
+      </c>
+      <c r="U126" t="n">
+        <v>83001</v>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>76bd8e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>867be7ff-5232-459e-8021-5043060b1661</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:45:16+03:00</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:47:26+03:00</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>suite:test-phase-00-plan</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Plan the test suite for examples/single-us/US-tags.md</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>/testing suite examples/single-us/US-tags.md --runner 0b7cb18f944dd65127f72bc1</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="n">
+        <v>38</v>
+      </c>
+      <c r="R127" t="n">
+        <v>1006033</v>
+      </c>
+      <c r="S127" t="n">
+        <v>11105</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.7997774</v>
+      </c>
+      <c r="U127" t="n">
+        <v>128082</v>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>eee03561-512c-45bc-b52f-e487ee6ff34a</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:47:34+03:00</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:57:47+03:00</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>suite:test-phase-01</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Every operation in the swagger (`loops/backend-dev/outputs/openapi.json`, 41 operations, including the two this</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>/testing suite examples/single-us/US-tags.md --runner 0b7cb18f944dd65127f72bc1</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>loops/testing/state/002-us-tags/suite.json</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>122</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6057298</v>
+      </c>
+      <c r="S128" t="n">
+        <v>69932</v>
+      </c>
+      <c r="T128" t="n">
+        <v>3.6315686</v>
+      </c>
+      <c r="U128" t="n">
+        <v>610913</v>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>914ca22</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>92b79e7d-5599-4e82-82f2-7443a13e5847</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:57:56+03:00</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-27T00:06:23+03:00</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>suite:test-phase-02</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>US1 (`US-TAGS-1`) is checked end to end: its acceptance criteria AC-US1-1..6, FR-001..FR-008 and BR-T1..BR-T4 through</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>/testing suite examples/single-us/US-tags.md --runner 0b7cb18f944dd65127f72bc1</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>loops/testing/state/002-us-tags/suite.json</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>138</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6077141</v>
+      </c>
+      <c r="S129" t="n">
+        <v>36739</v>
+      </c>
+      <c r="T129" t="n">
+        <v>2.688047399999999</v>
+      </c>
+      <c r="U129" t="n">
+        <v>504279</v>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>ac0dd20</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>b1cfb0f6-3ed7-436f-a10c-91a763a87e9a</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>orch-20260926T225858-388446</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>91be504</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-09-27T00:06:49+03:00</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-27T00:11:56+03:00</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>suite:test-phase-regression</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Every phase-mode check of feature `002-us-tags` is run again, unchanged, on the runner's fresh test database, plus</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>/testing suite examples/single-us/US-tags.md --runner 0b7cb18f944dd65127f72bc1</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>loops/testing/state/002-us-tags/suite.json</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>86</v>
+      </c>
+      <c r="R130" t="n">
+        <v>3206168</v>
+      </c>
+      <c r="S130" t="n">
+        <v>28451</v>
+      </c>
+      <c r="T130" t="n">
+        <v>1.8800248</v>
+      </c>
+      <c r="U130" t="n">
+        <v>304399</v>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>318fbaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1e3ca7a9-a840-4249-a554-0f56781a1740</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>20260924T160346-94745</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>414f8cf</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:03:46+03:00</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:11:12+03:00</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>phase-00-plan</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Plan backend from examples/single-us/US-tags.md</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 97160f9247edc94dfd81cf44</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-00-review.md</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>76</v>
+      </c>
+      <c r="R131" t="n">
+        <v>3359737</v>
+      </c>
+      <c r="S131" t="n">
+        <v>43372</v>
+      </c>
+      <c r="T131" t="n">
+        <v>2.5735112</v>
+      </c>
+      <c r="U131" t="n">
+        <v>439562</v>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ce45db66-6092-46a3-8db7-9ecf280d915e</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>20260924T161844-98093</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>a71a377</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:18:47+03:00</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:21:22+03:00</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>phase-00-plan</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 86451615feb94c52ac9b019c</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-00-review.md</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>38</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1359188</v>
+      </c>
+      <c r="S132" t="n">
+        <v>12722</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1.2770704</v>
+      </c>
+      <c r="U132" t="n">
+        <v>150951</v>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>3bfaaf87-44d9-4d25-a500-0dc7b8082a93</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>20260924T161844-98093</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>a71a377</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:21:24+03:00</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:22:38+03:00</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 86451615feb94c52ac9b019c</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>24</v>
+      </c>
+      <c r="R133" t="n">
+        <v>620935</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5800</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5523610000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>69606</v>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>85ec4372-37e1-4cbc-8abe-fc2418e1a031</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>20260924T161844-98093</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>a71a377</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:22:43+03:00</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:24:16+03:00</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>implement</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 86451615feb94c52ac9b019c</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>22</v>
+      </c>
+      <c r="R134" t="n">
+        <v>600747</v>
+      </c>
+      <c r="S134" t="n">
+        <v>7874</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.6108397999999999</v>
+      </c>
+      <c r="U134" t="n">
+        <v>88976</v>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>01702234-ea3f-41bd-bbff-244df7cc06d9</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>20260924T162625-101563</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>caf40ba</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:26:28+03:00</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:34:10+03:00</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>implement</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 304702a8f9e6acce8ebd0a40</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>90</v>
+      </c>
+      <c r="R135" t="n">
+        <v>3234266</v>
+      </c>
+      <c r="S135" t="n">
+        <v>19369</v>
+      </c>
+      <c r="T135" t="n">
+        <v>1.6177836</v>
+      </c>
+      <c r="U135" t="n">
+        <v>457953</v>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>210e4286-d479-4dea-a9f9-57dbc44f55ae</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>20260924T163914-107873</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>caf40ba</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:39:17+03:00</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:41:20+03:00</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>implement</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 8dd086dac613f66e2bd8e45f</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>26</v>
+      </c>
+      <c r="R136" t="n">
+        <v>635640</v>
+      </c>
+      <c r="S136" t="n">
+        <v>4266</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.4795694000000001</v>
+      </c>
+      <c r="U136" t="n">
+        <v>118987</v>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>283a9f7b-6458-4b49-a26e-a606c25b4840</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>20260924T163914-107873</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>caf40ba</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:41:41+03:00</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:43:42+03:00</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>backend-dev:phase-01</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>/testing phase backend-dev phase-01 --runner 8dd086dac613f66e2bd8e45f</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-01.md; loops/testing/runs/001-us-tags/backend-dev/phase-01/attempt-1/unit/unit-result.json</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>44</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1156172</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10454</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.7427248000000002</v>
+      </c>
+      <c r="U137" t="n">
+        <v>116637</v>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>d27f1f22-4e72-4b71-ba1d-7e7bf7fcfce0</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>20260924T163914-107873</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>caf40ba</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:43:45+03:00</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:44:34+03:00</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 8dd086dac613f66e2bd8e45f</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>18</v>
+      </c>
+      <c r="R138" t="n">
+        <v>380694</v>
+      </c>
+      <c r="S138" t="n">
+        <v>3431</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3270622</v>
+      </c>
+      <c r="U138" t="n">
+        <v>44308</v>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>51c04a05-8258-4f75-9027-a5da5f5817cb</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>20260924T163914-107873</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>caf40ba</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:44:36+03:00</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:46:12+03:00</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>dev</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>retry</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>2</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>/backend-dev examples/single-us/US-tags.md --runner 8dd086dac613f66e2bd8e45f</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md; loops/backend-dev/outputs/001-us-tags/phase-01-report.md</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>30</v>
+      </c>
+      <c r="R139" t="n">
+        <v>807203</v>
+      </c>
+      <c r="S139" t="n">
+        <v>6053</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.6097760000000001</v>
+      </c>
+      <c r="U139" t="n">
+        <v>91836</v>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>83aba213-08c7-491a-a2cf-c23f78f0d607</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>20260924T163914-107873</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>caf40ba</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:46:33+03:00</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:47:35+03:00</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>phase</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>backend-dev:phase-01</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>2</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>/testing phase backend-dev phase-01 --runner 8dd086dac613f66e2bd8e45f</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>loops/backend-dev/outputs/001-us-tags/phase-01.md; loops/testing/runs/001-us-tags/backend-dev/phase-01/attempt-2/unit/unit-result.json</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>22</v>
+      </c>
+      <c r="R140" t="n">
+        <v>521714</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5707</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.4796134</v>
+      </c>
+      <c r="U140" t="n">
+        <v>57503</v>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
           <t>28842f6d-5fc8-40f9-b22c-38944bd29b6d</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>dry-run</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>20260924T163914-107873</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>caf40ba</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>2026-09-24T16:47:39+03:00</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F141" t="inlineStr">
         <is>
           <t>2026-09-24T16:48:18+03:00</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G141" t="inlineStr">
         <is>
           <t>backend-dev</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>dev</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I141" t="inlineStr">
         <is>
           <t>001-us-tags</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t>phase-01</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="K141" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="L116" t="n">
+      <c r="L141" t="n">
         <v>2</v>
       </c>
-      <c r="M116" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr">
+      <c r="N141" t="inlineStr">
         <is>
           <t>Configure the runner-scaffolded Spring Boot project in `backend/`: pinned dependencies and plugins, profiles, Clock bean.</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr">
+      <c r="O141" t="inlineStr">
         <is>
           <t>/backend-dev examples/single-us/US-tags.md --runner 8dd086dac613f66e2bd8e45f</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
+      <c r="P141" t="inlineStr">
         <is>
           <t>loops/backend-dev/outputs/001-us-tags/phase-01-review.md</t>
         </is>
       </c>
-      <c r="Q116" t="n">
+      <c r="Q141" t="n">
         <v>14</v>
       </c>
-      <c r="R116" t="n">
+      <c r="R141" t="n">
         <v>301844</v>
       </c>
-      <c r="S116" t="n">
+      <c r="S141" t="n">
         <v>2797</v>
       </c>
-      <c r="T116" t="n">
+      <c r="T141" t="n">
         <v>0.3614408000000001</v>
       </c>
-      <c r="U116" t="n">
+      <c r="U141" t="n">
         <v>35849</v>
       </c>
-      <c r="V116" t="inlineStr">
+      <c r="V141" t="inlineStr">
         <is>
           <t>success</t>
         </is>
       </c>
-      <c r="W116" t="inlineStr"/>
+      <c r="W141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12488,7 +15081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -15070,7 +17663,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -15080,7 +17673,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-09-24T09:16:51.077Z</t>
+          <t>2026-09-26T19:21:31.546Z</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15090,14 +17683,14 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>i wanna to reveiw every task before execute</t>
+          <t>summary abouts commits</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -15107,7 +17700,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-09-24T09:17:54.811Z</t>
+          <t>2026-09-26T19:22:44.513Z</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -15117,14 +17710,14 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[Request interrupted by user for tool use]</t>
+          <t>push all</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -15134,24 +17727,24 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-09-24T09:18:19.122Z</t>
+          <t>2026-09-26T19:23:49.928Z</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>i wanna review every commit before push</t>
+          <t>[Request interrupted by user for tool use]</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -15161,7 +17754,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-09-24T09:19:06.042Z</t>
+          <t>2026-09-26T19:23:55.246Z</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -15171,14 +17764,14 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[Request interrupted by user for tool use]</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -15188,24 +17781,24 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-09-24T09:19:44.386Z</t>
+          <t>2026-09-26T19:24:56.039Z</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>are you update the plan that i sent to you</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -15215,24 +17808,24 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-09-24T09:20:42.716Z</t>
+          <t>2026-09-26T19:25:42.763Z</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>i wanna update exist plan</t>
+          <t>push</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -15242,7 +17835,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-09-24T09:21:48.183Z</t>
+          <t>2026-09-26T19:28:24.302Z</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -15252,14 +17845,14 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[Request interrupted by user for tool use]</t>
+          <t>resolve the two points</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -15269,7 +17862,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-09-24T09:31:08.620Z</t>
+          <t>2026-09-26T19:30:09.271Z</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -15279,14 +17872,14 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>can you make the testing in separated loop</t>
+          <t>answer the questions and complete</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -15296,7 +17889,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-09-24T09:32:56.128Z</t>
+          <t>2026-09-26T19:33:52.659Z</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -15306,14 +17899,14 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[Request interrupted by user for tool use]</t>
+          <t>force answer the questions and complete</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -15323,24 +17916,24 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-09-24T09:33:46.500Z</t>
+          <t>2026-09-26T19:35:14.567Z</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>i wanna update summarize-this-plan-dazzling-sun.md</t>
+          <t>solve point 2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -15350,7 +17943,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-09-24T09:37:41.527Z</t>
+          <t>2026-09-26T19:36:10.775Z</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -15360,14 +17953,14 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>i wanna a third loop that have testing not test loops</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -15377,24 +17970,24 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-09-24T09:42:40.327Z</t>
+          <t>2026-09-26T19:36:44.605Z</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>compare to this plan Backend &amp; Frontend DEVs Task One.txt</t>
+          <t>push</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -15404,7 +17997,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-09-24T09:46:07.702Z</t>
+          <t>2026-09-26T19:37:43.655Z</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -15414,14 +18007,14 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>is discussion before each phase implemented noted</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -15431,24 +18024,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-09-24T09:47:08.926Z</t>
+          <t>2026-09-26T19:47:41.988Z</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>i wanna add review before each phase implemented</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -15458,7 +18051,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-09-24T09:48:48.904Z</t>
+          <t>2026-09-26T19:50:21.759Z</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -15468,14 +18061,14 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>is unit test in the bakend noted</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -15485,7 +18078,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-09-24T09:49:10.828Z</t>
+          <t>2026-09-26T19:54:40.393Z</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -15495,14 +18088,14 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>how loops will be implemented</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -15512,24 +18105,24 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-09-24T09:50:18.902Z</t>
+          <t>2026-09-26T19:57:24.637Z</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>i wanna to explain speckit in every step you use to learn about it</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -15539,24 +18132,24 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-09-24T10:25:29.164Z</t>
+          <t>2026-09-26T20:01:41.699Z</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>planning</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>compare the updated plan with this plan Backend &amp; Frontend DEVs Task One.txt</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -15566,7 +18159,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-09-24T10:30:31.622Z</t>
+          <t>2026-09-26T20:05:29.010Z</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15576,14 +18169,14 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>solve point 3</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -15593,7 +18186,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-09-24T10:31:34.517Z</t>
+          <t>2026-09-26T20:23:08.324Z</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15603,14 +18196,14 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>solve point 4</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -15620,7 +18213,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-09-24T10:32:22.723Z</t>
+          <t>2026-09-26T20:28:23.791Z</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15630,14 +18223,14 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>solve point 6, 7</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -15647,24 +18240,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-09-24T10:33:21.882Z</t>
+          <t>2026-09-26T20:32:01.037Z</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>review the plan</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -15674,7 +18267,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-09-24T10:38:10.571Z</t>
+          <t>2026-09-26T20:40:09.148Z</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15684,14 +18277,14 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>resolve all points</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -15701,24 +18294,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-09-24T10:42:15.703Z</t>
+          <t>2026-09-26T20:41:47.211Z</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>review the plan again</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -15728,7 +18321,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-09-24T10:44:44.461Z</t>
+          <t>2026-09-26T20:47:43.708Z</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15738,14 +18331,14 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>resolve the points</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -15755,24 +18348,24 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-09-24T10:46:45.332Z</t>
+          <t>2026-09-26T20:51:17.941Z</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>review the plan again</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -15782,24 +18375,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-09-24T10:49:48.684Z</t>
+          <t>2026-09-26T20:53:54.824Z</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>review the plan again</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -15809,7 +18402,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-09-24T10:50:52.433Z</t>
+          <t>2026-09-26T21:01:59.003Z</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15819,14 +18412,14 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>resolve the points</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -15836,24 +18429,24 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-09-24T10:54:21.517Z</t>
+          <t>2026-09-26T21:05:21.070Z</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>review and resolve the points</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -15863,24 +18456,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-09-24T11:09:46.808Z</t>
+          <t>2026-09-26T21:06:53.965Z</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>review against this Backend &amp; Frontend DEVs Task One.txt</t>
+          <t>complete any pending point</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -15890,24 +18483,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-09-24T11:25:39.892Z</t>
+          <t>2026-09-26T21:07:20.916Z</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>review against this Backend &amp; Frontend DEVs Task One.txt</t>
+          <t>push</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+          <t>e466a1bd-03da-4c5e-861c-b7b8f67f39c7</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -15917,7 +18510,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-09-24T11:27:26.226Z</t>
+          <t>2026-09-26T21:17:45.937Z</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15927,7 +18520,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>solve the points</t>
+          <t>push</t>
         </is>
       </c>
     </row>
@@ -15944,17 +18537,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-09-24T11:32:39.076Z</t>
+          <t>2026-09-24T09:16:51.077Z</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>review the plan</t>
+          <t>i wanna to reveiw every task before execute</t>
         </is>
       </c>
     </row>
@@ -15971,7 +18564,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-09-24T11:34:15.242Z</t>
+          <t>2026-09-24T09:17:54.811Z</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15981,7 +18574,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>[Request interrupted by user for tool use]</t>
         </is>
       </c>
     </row>
@@ -15998,7 +18591,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-09-24T11:35:51.607Z</t>
+          <t>2026-09-24T09:18:19.122Z</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -16008,7 +18601,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>review the plan</t>
+          <t>i wanna review every commit before push</t>
         </is>
       </c>
     </row>
@@ -16025,7 +18618,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-09-24T11:37:13.217Z</t>
+          <t>2026-09-24T09:19:06.042Z</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -16035,7 +18628,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>[Request interrupted by user for tool use]</t>
         </is>
       </c>
     </row>
@@ -16052,17 +18645,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-09-24T11:38:29.585Z</t>
+          <t>2026-09-24T09:19:44.386Z</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>review the plan</t>
+          <t>are you update the plan that i sent to you</t>
         </is>
       </c>
     </row>
@@ -16079,17 +18672,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-09-24T11:39:23.253Z</t>
+          <t>2026-09-24T09:20:42.716Z</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>building loops</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>i wanna update exist plan</t>
         </is>
       </c>
     </row>
@@ -16106,7 +18699,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-09-24T11:41:23.721Z</t>
+          <t>2026-09-24T09:21:48.183Z</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16133,17 +18726,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-09-24T11:41:33.379Z</t>
+          <t>2026-09-24T09:31:08.620Z</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>building loops</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>review all the plan</t>
+          <t>can you make the testing in separated loop</t>
         </is>
       </c>
     </row>
@@ -16160,7 +18753,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-09-24T11:46:20.256Z</t>
+          <t>2026-09-24T09:32:56.128Z</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16170,7 +18763,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>resolve</t>
+          <t>[Request interrupted by user for tool use]</t>
         </is>
       </c>
     </row>
@@ -16187,17 +18780,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-09-24T11:48:16.155Z</t>
+          <t>2026-09-24T09:33:46.500Z</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>building loops</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>make playwrite headless</t>
+          <t>i wanna update summarize-this-plan-dazzling-sun.md</t>
         </is>
       </c>
     </row>
@@ -16214,7 +18807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-09-24T11:49:29.075Z</t>
+          <t>2026-09-24T09:37:41.527Z</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16224,7 +18817,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>add rule to dont make anything that you dont know</t>
+          <t>i wanna a third loop that have testing not test loops</t>
         </is>
       </c>
     </row>
@@ -16241,7 +18834,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-09-24T11:51:15.600Z</t>
+          <t>2026-09-24T09:42:40.327Z</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16251,7 +18844,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>is the plan ready for implement</t>
+          <t>compare to this plan Backend &amp; Frontend DEVs Task One.txt</t>
         </is>
       </c>
     </row>
@@ -16268,7 +18861,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-09-24T11:51:46.259Z</t>
+          <t>2026-09-24T09:46:07.702Z</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -16278,32 +18871,896 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>[Request interrupted by user for tool use]</t>
+          <t>is discussion before each phase implemented noted</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:47:08.926Z</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>i wanna add review before each phase implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:48:48.904Z</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>is unit test in the bakend noted</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:49:10.828Z</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>how loops will be implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:50:18.902Z</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>planning</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>i wanna to explain speckit in every step you use to learn about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:25:29.164Z</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>planning</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>compare the updated plan with this plan Backend &amp; Frontend DEVs Task One.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:30:31.622Z</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>solve point 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:31:34.517Z</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>solve point 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:32:22.723Z</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>solve point 6, 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:33:21.882Z</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>review the plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:38:10.571Z</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>resolve all points</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:42:15.703Z</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>review the plan again</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:44:44.461Z</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>resolve the points</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:46:45.332Z</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>review the plan again</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:49:48.684Z</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>review the plan again</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:50:52.433Z</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>resolve the points</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-09-24T10:54:21.517Z</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>review and resolve the points</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:09:46.808Z</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>review against this Backend &amp; Frontend DEVs Task One.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:25:39.892Z</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>review against this Backend &amp; Frontend DEVs Task One.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:27:26.226Z</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>solve the points</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:32:39.076Z</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>review the plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:34:15.242Z</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>resolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:35:51.607Z</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>review the plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:37:13.217Z</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>resolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:38:29.585Z</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>review the plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:39:23.253Z</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>resolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:41:23.721Z</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>[Request interrupted by user for tool use]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:41:33.379Z</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>review all the plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:46:20.256Z</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>resolve</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:48:16.155Z</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>make playwrite headless</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:49:29.075Z</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>add rule to dont make anything that you dont know</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:51:15.600Z</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>planning</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>is the plan ready for implement</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>e9418ca6-5abb-4e40-a649-c18868e62099</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>-home-eslam-Downloads-TTFolder</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-09-24T11:51:46.259Z</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>building loops</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>[Request interrupted by user for tool use]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>fddacf0e-976f-4a2e-a3cf-dee5332de041</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>-home-eslam-Downloads-TTFolder-quickflow-dryrun</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>2026-09-24T13:25:03.499Z</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>debugging</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>Answer in 4 short lines, no other text. 1) Run the Bash command: cd backend &amp;&amp; ./mvnw -v | head -1   and print its first output line or the exact error. 2) List the names of every MCP tool you have that starts with mcp__ (just the server prefixes). 3) Do you see instructions mentioning lean-ctx or ctx_read in your context? yes/no. 4) Which CLAUDE.md files are in your context (paths)?</t>
         </is>
@@ -16320,7 +19777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17772,12 +21229,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -17792,19 +21249,19 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G34" t="n">
-        <v>4718925</v>
+        <v>4417927</v>
       </c>
       <c r="H34" t="n">
-        <v>56094</v>
+        <v>54774</v>
       </c>
       <c r="I34" t="n">
-        <v>3.8506</v>
+        <v>3.2994</v>
       </c>
       <c r="J34" t="n">
-        <v>590513</v>
+        <v>546565</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -17815,41 +21272,514 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>frontend-dev:phase-00-plan</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>90</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3341953</v>
+      </c>
+      <c r="H35" t="n">
+        <v>35833</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.419</v>
+      </c>
+      <c r="J35" t="n">
+        <v>367592</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>orchestrator:plan</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14</v>
+      </c>
+      <c r="G36" t="n">
+        <v>251265</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2517</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2413</v>
+      </c>
+      <c r="J36" t="n">
+        <v>30053</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>backend-dev:phase-01</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>164</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6087352</v>
+      </c>
+      <c r="H37" t="n">
+        <v>62105</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5.7026</v>
+      </c>
+      <c r="J37" t="n">
+        <v>651299</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>frontend-dev:phase-01</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>212</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7058458</v>
+      </c>
+      <c r="H38" t="n">
+        <v>47770</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.2231</v>
+      </c>
+      <c r="J38" t="n">
+        <v>610636</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>backend-dev:phase-02</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>180</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6187869</v>
+      </c>
+      <c r="H39" t="n">
+        <v>55055</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.2072</v>
+      </c>
+      <c r="J39" t="n">
+        <v>696093</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>frontend-dev:phase-02</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>184</v>
+      </c>
+      <c r="G40" t="n">
+        <v>5387762</v>
+      </c>
+      <c r="H40" t="n">
+        <v>41081</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.4472</v>
+      </c>
+      <c r="J40" t="n">
+        <v>506124</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>testing:suite:test-phase-00-plan</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>38</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1006033</v>
+      </c>
+      <c r="H41" t="n">
+        <v>11105</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7998</v>
+      </c>
+      <c r="J41" t="n">
+        <v>128082</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>testing:suite:test-phase-01</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>122</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6057298</v>
+      </c>
+      <c r="H42" t="n">
+        <v>69932</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.6316</v>
+      </c>
+      <c r="J42" t="n">
+        <v>610913</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>testing:suite:test-phase-02</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>138</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6077141</v>
+      </c>
+      <c r="H43" t="n">
+        <v>36739</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="J43" t="n">
+        <v>504279</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>testing:suite:test-phase-regression</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>86</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3206168</v>
+      </c>
+      <c r="H44" t="n">
+        <v>28451</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J44" t="n">
+        <v>304399</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>dry-run</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>001-us-tags</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>backend-dev:phase-00-plan</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>114</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4718925</v>
+      </c>
+      <c r="H45" t="n">
+        <v>56094</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3.8506</v>
+      </c>
+      <c r="J45" t="n">
+        <v>590513</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>backend-dev:phase-01</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D46" t="n">
         <v>9</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E46" t="n">
         <v>2</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F46" t="n">
         <v>290</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G46" t="n">
         <v>8259215</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H46" t="n">
         <v>65751</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I46" t="n">
         <v>5.7812</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J46" t="n">
         <v>1081655</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>success</t>
         </is>
@@ -18014,22 +21944,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
-        <v>1244</v>
+        <v>1600</v>
       </c>
       <c r="F4" t="n">
-        <v>49883600</v>
+        <v>63129031</v>
       </c>
       <c r="G4" t="n">
-        <v>470747</v>
+        <v>598986</v>
       </c>
       <c r="H4" t="n">
-        <v>47.4918</v>
+        <v>58.0638</v>
       </c>
       <c r="I4" t="n">
-        <v>5155328</v>
+        <v>6579448</v>
       </c>
     </row>
     <row r="5">
@@ -18049,22 +21979,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E5" t="n">
-        <v>1226</v>
+        <v>1542</v>
       </c>
       <c r="F5" t="n">
-        <v>39752986</v>
+        <v>49615099</v>
       </c>
       <c r="G5" t="n">
-        <v>379462</v>
+        <v>464546</v>
       </c>
       <c r="H5" t="n">
-        <v>34.2464</v>
+        <v>41.2349</v>
       </c>
       <c r="I5" t="n">
-        <v>4949364</v>
+        <v>5959114</v>
       </c>
     </row>
     <row r="6">
@@ -18084,22 +22014,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>742643</v>
+        <v>993908</v>
       </c>
       <c r="G6" t="n">
-        <v>8092</v>
+        <v>10609</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7752</v>
+        <v>1.0166</v>
       </c>
       <c r="I6" t="n">
-        <v>95197</v>
+        <v>125250</v>
       </c>
     </row>
     <row r="7">
@@ -18119,22 +22049,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>1538</v>
+        <v>1808</v>
       </c>
       <c r="F7" t="n">
-        <v>59786740</v>
+        <v>69160517</v>
       </c>
       <c r="G7" t="n">
-        <v>534244</v>
+        <v>617539</v>
       </c>
       <c r="H7" t="n">
-        <v>34.986</v>
+        <v>40.7239</v>
       </c>
       <c r="I7" t="n">
-        <v>6336986</v>
+        <v>7281425</v>
       </c>
     </row>
     <row r="8">
@@ -18154,22 +22084,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>900</v>
+        <v>1284</v>
       </c>
       <c r="F8" t="n">
-        <v>38937844</v>
+        <v>55284484</v>
       </c>
       <c r="G8" t="n">
-        <v>350051</v>
+        <v>496278</v>
       </c>
       <c r="H8" t="n">
-        <v>22.9228</v>
+        <v>31.9223</v>
       </c>
       <c r="I8" t="n">
-        <v>4600927</v>
+        <v>6148600</v>
       </c>
     </row>
     <row r="9">
@@ -18181,22 +22111,22 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="E9" t="n">
-        <v>5350</v>
+        <v>6690</v>
       </c>
       <c r="F9" t="n">
-        <v>202081953</v>
+        <v>251161179</v>
       </c>
       <c r="G9" t="n">
-        <v>1864441</v>
+        <v>2309803</v>
       </c>
       <c r="H9" t="n">
-        <v>150.0539</v>
+        <v>182.5932</v>
       </c>
       <c r="I9" t="n">
-        <v>22809970</v>
+        <v>27766005</v>
       </c>
     </row>
     <row r="11">
@@ -18206,7 +22136,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -18236,7 +22166,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15">
@@ -18247,7 +22177,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-26T22:15:27</t>
+          <t>2026-09-27T00:19:02</t>
         </is>
       </c>
     </row>
@@ -18262,7 +22192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -19256,32 +23186,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-24T16:16:36+03:00</t>
+          <t>2026-09-26T22:23:24+03:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>backend-dev</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>001-us-tags</t>
-        </is>
-      </c>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>phase-00</t>
+          <t>122 commits</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>commit</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -19291,7 +23217,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Q1: yes, minimal Task in this feature: id + title (required, not blank, &lt;= 200 chars); POST /api/tasks, GET /api/tasks/{id}, GET /api/tasks; no edit/delete/status/priority/due date. Q2: trim and lower-case tags (Locale.ROOT); the API returns the lower-case form. (entered through Claude on the user's behalf)</t>
+          <t>bulk approval: user said "push all" in Claude Code (recorded by Claude)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -19300,12 +23226,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-24T16:22:40+03:00</t>
+          <t>2026-09-26T22:47:11+03:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -19315,12 +23241,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>phase-01</t>
+          <t>phase-00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -19330,41 +23256,41 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>approve</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Q1: tags are always lower case (stored, matched, filtered and shown as lower case). Q2: adding a tag the task already has is a silent no-op (200, task unchanged, counts once toward the 10). Q3: removing a tag the task doesn't have is a silent no-op (200, task unchanged); an unknown task id is still 404. (answered by the user; entered by Claude)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>85ec4372-37e1-4cbc-8abe-fc2418e1a031</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-24T16:26:17+03:00</t>
+          <t>2026-09-26T22:54:41+03:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>backend-dev</t>
+          <t>frontend-dev</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>phase-01</t>
+          <t>phase-00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -19374,30 +23300,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>approve</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Q1: the ./mvnw block was a runner bug (user-level hooks leaked into loop sessions), fixed in engine 0a12306; ./mvnw now runs in loop sessions. Look up the latest jacoco-maven-plugin (Java 25 support) and springdoc-openapi-maven-plugin releases through ./mvnw (e.g. the versions or help plugin against Maven Central), pin them in pom.xml as the constitution says, and continue T001-T005. (tooling answer entered by Claude during the dry run)</t>
-        </is>
-      </c>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>01702234-ea3f-41bd-bbff-244df7cc06d9</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dry-run</t>
+          <t>run</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-24T16:39:06+03:00</t>
+          <t>2026-09-26T23:01:06+03:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -19407,7 +23325,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>001-us-tags</t>
+          <t>002-us-tags</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -19422,16 +23340,328 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>approve</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Q2: the JDK 25 compiler is now installed (java-25-openjdk-devel, javac 25.0.4.1 in /usr/lib/jvm/java-25-openjdk). Keep java.version 25, run L.build and L.test, and continue phase-01. (tooling answer entered by Claude during the dry run)</t>
-        </is>
-      </c>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>90173efa-debc-4995-9bae-1df8951608ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:13:34+03:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>e47ecef3-ccbf-4dd1-9b11-7d5a3942b564</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:25:26+03:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>phase-02</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6b837034-1456-41ea-b432-34d3050f5b87</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:37:46+03:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>frontend-dev</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>002-us-tags</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>phase-02</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>9bb2c683-0517-4568-858e-c5c37825e41f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:16:36+03:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>phase-00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>approve</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Q1: yes, minimal Task in this feature: id + title (required, not blank, &lt;= 200 chars); POST /api/tasks, GET /api/tasks/{id}, GET /api/tasks; no edit/delete/status/priority/due date. Q2: trim and lower-case tags (Locale.ROOT); the API returns the lower-case form. (entered through Claude on the user's behalf)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:22:40+03:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>85ec4372-37e1-4cbc-8abe-fc2418e1a031</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:26:17+03:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>approve</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Q1: the ./mvnw block was a runner bug (user-level hooks leaked into loop sessions), fixed in engine 0a12306; ./mvnw now runs in loop sessions. Look up the latest jacoco-maven-plugin (Java 25 support) and springdoc-openapi-maven-plugin releases through ./mvnw (e.g. the versions or help plugin against Maven Central), pin them in pom.xml as the constitution says, and continue T001-T005. (tooling answer entered by Claude during the dry run)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>01702234-ea3f-41bd-bbff-244df7cc06d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dry-run</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:39:06+03:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>001-us-tags</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>phase-01</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>approve</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Q2: the JDK 25 compiler is now installed (java-25-openjdk-devel, javac 25.0.4.1 in /usr/lib/jvm/java-25-openjdk). Keep java.version 25, run L.build and L.test, and continue phase-01. (tooling answer entered by Claude during the dry run)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
         <is>
           <t>210e4286-d479-4dea-a9f9-57dbc44f55ae</t>
         </is>
